--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>66.04870357559842</v>
+        <v>10.73291433103474</v>
       </c>
       <c r="D2" t="n">
-        <v>65.99082217741412</v>
+        <v>10.72350860382979</v>
       </c>
       <c r="E2" t="n">
-        <v>3.171346662371685</v>
+        <v>0.5153438326353987</v>
       </c>
       <c r="F2" t="n">
-        <v>3.147993031760452</v>
+        <v>0.5115488676610732</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.08436888387826</v>
+        <v>9.601209943630217</v>
       </c>
       <c r="D3" t="n">
-        <v>59.06474378064409</v>
+        <v>9.598020864354666</v>
       </c>
       <c r="E3" t="n">
-        <v>3.171346662371685</v>
+        <v>0.5153438326353987</v>
       </c>
       <c r="F3" t="n">
-        <v>3.147993031760452</v>
+        <v>0.5115488676610732</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>59.58626608015637</v>
+        <v>9.68276823802541</v>
       </c>
       <c r="D4" t="n">
-        <v>59.59240410954695</v>
+        <v>9.68376566780138</v>
       </c>
       <c r="E4" t="n">
-        <v>3.171346662371685</v>
+        <v>0.5153438326353987</v>
       </c>
       <c r="F4" t="n">
-        <v>3.147993031760452</v>
+        <v>0.5115488676610732</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
